--- a/13-06-26/Zahid.xlsx
+++ b/13-06-26/Zahid.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{907E8A9F-8B0E-465B-A9C8-1EF95AEA7008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BB6683C-4B1C-44BC-999E-F1944B6E85CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23134,22 +23134,22 @@
   <sheetFormatPr defaultColWidth="29.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.453125" customWidth="1"/>
-    <col min="3" max="3" width="5.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.54296875" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="6.54296875" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="5.54296875" customWidth="1"/>
+    <col min="6" max="6" width="6.54296875" customWidth="1"/>
     <col min="7" max="7" width="4" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8.984375E-2" customWidth="1"/>
-    <col min="10" max="10" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.453125" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="7.453125" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="8" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="10" style="69" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="9.54296875" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="9.7265625" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="4.54296875" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="7.26953125" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="7.453125" customWidth="1"/>
+    <col min="11" max="11" width="9.453125" customWidth="1"/>
+    <col min="12" max="12" width="7.453125" customWidth="1"/>
+    <col min="13" max="13" width="8" customWidth="1"/>
+    <col min="14" max="14" width="10" style="69" customWidth="1"/>
+    <col min="15" max="15" width="9.54296875" customWidth="1"/>
+    <col min="16" max="16" width="9.7265625" customWidth="1"/>
+    <col min="17" max="17" width="4.54296875" customWidth="1"/>
+    <col min="18" max="18" width="7.26953125" customWidth="1"/>
     <col min="20" max="20" width="61.6328125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="10.453125" bestFit="1" customWidth="1"/>
   </cols>
@@ -24566,7 +24566,7 @@
     <mergeCell ref="N12:P12"/>
     <mergeCell ref="A14:B15"/>
   </mergeCells>
-  <dataValidations disablePrompts="1" count="3">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N9:P9" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>$XFD$12:$XFD$17</formula1>
     </dataValidation>
@@ -24581,7 +24581,7 @@
   <pageSetup scale="10" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0200-000003000000}">
           <x14:formula1>
             <xm:f>Sheet2!$B$5:$B$10</xm:f>
